--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487662_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487662_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GOMA</t>
+          <t>M. ESTAPE ROIZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2751</v>
+        <v>5.3077</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1542</v>
+        <v>3.0341</v>
       </c>
       <c r="F2" t="n">
-        <v>4.1209</v>
+        <v>2.2736</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6255</v>
+        <v>2.3674</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1495</v>
+        <v>0.6912</v>
       </c>
       <c r="I2" t="n">
-        <v>0.476</v>
+        <v>1.6761</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4828</v>
+        <v>1.3514</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4016</v>
+        <v>0.0701</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08119999999999999</v>
+        <v>1.2813</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1427</v>
+        <v>1.016</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2521</v>
+        <v>0.6212</v>
       </c>
       <c r="O2" t="n">
         <v>0.3948</v>
       </c>
       <c r="P2" t="n">
-        <v>0.194</v>
+        <v>2.5224</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1045</v>
+        <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4556</v>
+        <v>-0.4761</v>
       </c>
       <c r="T2" t="n">
-        <v>1.6879</v>
+        <v>-0.4352</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7677</v>
+        <v>-0.0409</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W2" t="n">
-        <v>0.894</v>
+        <v>2.1179</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.894</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5314</v>
+        <v>5.1037</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1886</v>
+        <v>3.7883</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3427</v>
+        <v>1.3155</v>
       </c>
       <c r="G3" t="n">
         <v>5.6148</v>
@@ -688,13 +688,13 @@
         <v>2.1344</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5879</v>
+        <v>-1.0156</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4105</v>
+        <v>-0.8109</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1774</v>
+        <v>-0.2047</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6597</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ESTAPE ROIZ</t>
+          <t>G. GOMA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3834</v>
+        <v>4.6171</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5731</v>
+        <v>1.3139</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8103</v>
+        <v>3.3032</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3674</v>
+        <v>2.6255</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6912</v>
+        <v>2.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6761</v>
+        <v>0.476</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3514</v>
+        <v>2.4828</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0701</v>
+        <v>2.4016</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2813</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>1.016</v>
+        <v>0.1427</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6212</v>
+        <v>-0.2521</v>
       </c>
       <c r="O4" t="n">
         <v>0.3948</v>
       </c>
       <c r="P4" t="n">
-        <v>2.5224</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5224</v>
+        <v>3.1045</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4004</v>
+        <v>1.7976</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8962</v>
+        <v>0.8476</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5042</v>
+        <v>0.95</v>
       </c>
       <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
         <v>0.894</v>
       </c>
-      <c r="W4" t="n">
-        <v>2.1179</v>
-      </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. RUBIO CORCHADO</t>
+          <t>D. GARCIA DELGADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4666</v>
+        <v>3.642</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9538</v>
+        <v>1.2971</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5129</v>
+        <v>2.3448</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2554</v>
+        <v>1.8079</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8527</v>
+        <v>0.3353</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5973000000000001</v>
+        <v>1.4726</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9042</v>
+        <v>1.4477</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0289</v>
+        <v>0.103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8753</v>
+        <v>1.3447</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1596</v>
+        <v>0.3602</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8816000000000001</v>
+        <v>0.2323</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2781</v>
+        <v>0.1279</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1344</v>
+        <v>1.7463</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.1045</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3638</v>
+        <v>0.0878</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2042</v>
+        <v>-0.4327</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5204</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GARCIA DELGADO</t>
+          <t>G. TCHIRAKADZE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4329</v>
+        <v>3.2216</v>
       </c>
       <c r="E6" t="n">
-        <v>1.197</v>
+        <v>0.3823</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2358</v>
+        <v>2.8393</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8079</v>
+        <v>1.0392</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3353</v>
+        <v>1.1732</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4726</v>
+        <v>-0.134</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4477</v>
+        <v>0.3511</v>
       </c>
       <c r="K6" t="n">
-        <v>0.103</v>
+        <v>1.0134</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3447</v>
+        <v>-0.6623</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3602</v>
+        <v>0.6881</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2323</v>
+        <v>0.1598</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1279</v>
+        <v>0.5283</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>2.1344</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1214</v>
+        <v>0.1242</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0.1074</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4114</v>
+        <v>0.0168</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>0.894</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. TCHIRAKADZE</t>
+          <t>M. RUBIO CORCHADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2066</v>
+        <v>3.0484</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4218</v>
+        <v>0.7536</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7848</v>
+        <v>2.2948</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0392</v>
+        <v>-0.2554</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1732</v>
+        <v>-0.8527</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.134</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3511</v>
+        <v>0.9042</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0134</v>
+        <v>0.0289</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6623</v>
+        <v>0.8753</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6881</v>
+        <v>-1.1596</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1598</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5283</v>
+        <v>-0.2781</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1642</v>
+        <v>2.1344</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1344</v>
+        <v>3.1045</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1092</v>
+        <v>-0.0544</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1469</v>
+        <v>-0.4044</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0377</v>
+        <v>0.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="W7" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.182</v>
+        <v>1.6186</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6423</v>
+        <v>0.9426</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5397</v>
+        <v>0.676</v>
       </c>
       <c r="G8" t="n">
         <v>0.7111</v>
@@ -1078,13 +1078,13 @@
         <v>2.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5754</v>
+        <v>-0.1388</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5687</v>
+        <v>-0.2684</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0067</v>
+        <v>0.1296</v>
       </c>
       <c r="V8" t="n">
         <v>-0.894</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1386</v>
+        <v>1.4662</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4538</v>
+        <v>-0.1535</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5925</v>
+        <v>1.6197</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1667</v>
@@ -1156,13 +1156,13 @@
         <v>2.3284</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4305</v>
+        <v>-0.1029</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.387</v>
+        <v>-0.0867</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0435</v>
+        <v>-0.0162</v>
       </c>
       <c r="V9" t="n">
         <v>0.3776</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7099</v>
+        <v>1.1708</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1662</v>
+        <v>-1.7052</v>
       </c>
       <c r="F10" t="n">
         <v>2.8761</v>
@@ -1234,10 +1234,10 @@
         <v>2.7164</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6191</v>
+        <v>-0.1581</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7504</v>
+        <v>-0.2894</v>
       </c>
       <c r="U10" t="n">
         <v>0.1313</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.467</v>
+        <v>0.4031</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3222</v>
+        <v>0.122</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1448</v>
+        <v>0.2811</v>
       </c>
       <c r="G11" t="n">
         <v>0.8512</v>
@@ -1312,13 +1312,13 @@
         <v>2.1344</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2961</v>
+        <v>-0.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1469</v>
+        <v>-0.0533</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.443</v>
+        <v>-0.3067</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2821</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2137</v>
+        <v>0.3107</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9244</v>
+        <v>-0.5636</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7107</v>
+        <v>0.8742</v>
       </c>
       <c r="G12" t="n">
         <v>-1.753</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4607</v>
+        <v>0.0636</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2905</v>
+        <v>0.0704</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1702</v>
+        <v>-0.0067</v>
       </c>
       <c r="V12" t="n">
         <v>1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.5543</v>
+        <v>-1.5815</v>
       </c>
       <c r="E13" t="n">
         <v>-1.725</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1708</v>
+        <v>0.1435</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8205</v>
@@ -1468,13 +1468,13 @@
         <v>0.5821</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3457</v>
+        <v>-0.3729</v>
       </c>
       <c r="T13" t="n">
         <v>-0.2299</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.0255</v>
+        <v>28.3284</v>
       </c>
       <c r="E14" t="n">
-        <v>7.183600000000002</v>
+        <v>7.486600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>20.842</v>
+        <v>20.8418</v>
       </c>
       <c r="G14" t="n">
         <v>13.8744</v>
@@ -1546,13 +1546,13 @@
         <v>26.1944</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.9085999999999997</v>
+        <v>-0.6055999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2885</v>
+        <v>-1.9855</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.3799</v>
       </c>
       <c r="V14" t="n">
         <v>2.4477</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4785</v>
+        <v>4.3144</v>
       </c>
       <c r="E15" t="n">
-        <v>3.8485</v>
+        <v>3.1478</v>
       </c>
       <c r="F15" t="n">
-        <v>1.63</v>
+        <v>1.1666</v>
       </c>
       <c r="G15" t="n">
         <v>0.9092</v>
@@ -1624,13 +1624,13 @@
         <v>0.194</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4917</v>
+        <v>1.3277</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2864</v>
+        <v>0.5857</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2053</v>
+        <v>0.7419</v>
       </c>
       <c r="V15" t="n">
         <v>1.8836</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. MARTIN GONZALEZ</t>
+          <t>A. FERNÁNDEZ GÓMEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9201</v>
+        <v>-0.3844</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7955</v>
+        <v>0.8761</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8754</v>
+        <v>-1.2604</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9922</v>
+        <v>-3.4557</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3543</v>
+        <v>-2.7599</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6379</v>
+        <v>-0.6957</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1293</v>
+        <v>-0.7049</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5026</v>
+        <v>-1.9278</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6267</v>
+        <v>1.2229</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1371</v>
+        <v>-2.7508</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1483</v>
+        <v>-0.8321</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0111</v>
+        <v>-1.9187</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9702</v>
+        <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2862</v>
+        <v>0.1668</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6662</v>
+        <v>-0.4131</v>
       </c>
       <c r="U16" t="n">
-        <v>0.38</v>
+        <v>0.5799</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6119</v>
+        <v>1.7403</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.9641</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6119</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>A. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.8466</v>
+        <v>-0.4859</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2719</v>
+        <v>-1.5953</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.5746</v>
+        <v>1.1094</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1682</v>
+        <v>-0.9922</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.3479</v>
+        <v>-0.3543</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1796</v>
+        <v>-0.6379</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0062</v>
+        <v>-1.1293</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5849</v>
+        <v>-0.5026</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5911999999999999</v>
+        <v>-0.6267</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1744</v>
+        <v>0.1371</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7629</v>
+        <v>0.1483</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4115</v>
+        <v>-0.0111</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3217</v>
+        <v>0.1481</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6919999999999999</v>
+        <v>-0.466</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6297</v>
+        <v>0.6141</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. FERNÁNDEZ GÓMEZ</t>
+          <t>E. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.946</v>
+        <v>-2.1286</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1754</v>
+        <v>-2.7964</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1213</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.4557</v>
+        <v>-0.8431999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7599</v>
+        <v>-0.4317</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6957</v>
+        <v>-0.4115</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7049</v>
+        <v>-0.6261</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.9278</v>
+        <v>-0.6261</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2229</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7508</v>
+        <v>-0.2171</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8321</v>
+        <v>0.1944</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.9187</v>
+        <v>-0.4115</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1642</v>
+        <v>-1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1344</v>
+        <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3948</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1138</v>
+        <v>-0.2299</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.281</v>
+        <v>0.3028</v>
       </c>
       <c r="V18" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9641</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2096</v>
+        <v>-2.1647</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6938</v>
+        <v>-0.372</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5158</v>
+        <v>-1.7927</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.7351</v>
+        <v>-1.1682</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5083</v>
+        <v>-1.3479</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.2434</v>
+        <v>0.1796</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0822</v>
+        <v>0.0062</v>
       </c>
       <c r="K19" t="n">
-        <v>1.001</v>
+        <v>-0.5849</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8173</v>
+        <v>-1.1744</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4927</v>
+        <v>-0.7629</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.3246</v>
+        <v>-0.4115</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5523</v>
+        <v>-0.7761</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3284</v>
+        <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4076</v>
+        <v>1.0035</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4344</v>
+        <v>0.5919</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0269</v>
+        <v>0.4116</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3299</v>
+        <v>-1.2239</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3299</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. VIDAL RODRIGUEZ</t>
+          <t>P. SÁNCHEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.262</v>
+        <v>-2.6369</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7964</v>
+        <v>-2.1244</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5344</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-1.4066</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4317</v>
+        <v>1.656</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4115</v>
+        <v>-3.0625</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6261</v>
+        <v>0.7244</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6261</v>
+        <v>2.0185</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.2941</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2171</v>
+        <v>-2.131</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1944</v>
+        <v>-0.3625</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4115</v>
+        <v>-1.7685</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.3582</v>
+        <v>-1.7463</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0606</v>
+        <v>0.5159</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2299</v>
+        <v>0.0617</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1694</v>
+        <v>0.4542</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3576</v>
+        <v>-3.0056</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6495</v>
+        <v>-3.3492</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2919</v>
+        <v>0.3436</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1138</v>
@@ -2092,13 +2092,13 @@
         <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3214</v>
+        <v>0.0306</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3993</v>
+        <v>-0.099</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0779</v>
+        <v>0.1296</v>
       </c>
       <c r="V21" t="n">
         <v>0.6597</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. SÁNCHEZ GUTIERREZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4434</v>
+        <v>-3.0438</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5248</v>
+        <v>-3.1953</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9186</v>
+        <v>0.1515</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4066</v>
+        <v>-1.7351</v>
       </c>
       <c r="H22" t="n">
-        <v>1.656</v>
+        <v>0.5083</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0625</v>
+        <v>-2.2434</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7244</v>
+        <v>1.0822</v>
       </c>
       <c r="K22" t="n">
-        <v>2.0185</v>
+        <v>1.001</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2941</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.131</v>
+        <v>-2.8173</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3625</v>
+        <v>-0.4927</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7685</v>
+        <v>-2.3246</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7463</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9105</v>
+        <v>-3.8806</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2905</v>
+        <v>0.5734</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3387</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0482</v>
+        <v>0.6405</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5467</v>
+        <v>-3.2582</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.194</v>
+        <v>-2.7936</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3527</v>
+        <v>-0.4645</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8999</v>
@@ -2248,13 +2248,13 @@
         <v>1.5523</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5706</v>
+        <v>-0.2821</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.005</v>
+        <v>-0.6046</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5657</v>
+        <v>0.3225</v>
       </c>
       <c r="V23" t="n">
         <v>0.2821</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9558</v>
+        <v>-5.1766</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2128</v>
+        <v>-3.8124</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.743</v>
+        <v>-1.3643</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8331</v>
@@ -2326,13 +2326,13 @@
         <v>1.7463</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8302</v>
+        <v>-0.051</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8233</v>
+        <v>-0.4229</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0069</v>
+        <v>0.3718</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1283</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.0161</v>
+        <v>-6.7187</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.727</v>
+        <v>-4.8271</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.2891</v>
+        <v>-1.8916</v>
       </c>
       <c r="G25" t="n">
         <v>2.6644</v>
@@ -2404,13 +2404,13 @@
         <v>1.3582</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4419</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2165</v>
+        <v>-0.3166</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6584</v>
+        <v>1.056</v>
       </c>
       <c r="V25" t="n">
         <v>-3.7194</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-28.0254</v>
+        <v>-24.689</v>
       </c>
       <c r="E26" t="n">
         <v>-20.8418</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.183400000000001</v>
+        <v>-3.8472</v>
       </c>
       <c r="G26" t="n">
         <v>-13.8742</v>
@@ -2455,10 +2455,10 @@
         <v>-12.2347</v>
       </c>
       <c r="J26" t="n">
-        <v>2.3575</v>
+        <v>2.357500000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6087</v>
+        <v>3.608699999999999</v>
       </c>
       <c r="L26" t="n">
         <v>-1.2511</v>
@@ -2467,7 +2467,7 @@
         <v>-16.2318</v>
       </c>
       <c r="N26" t="n">
-        <v>-5.248</v>
+        <v>-5.247999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>-10.9835</v>
@@ -2476,22 +2476,22 @@
         <v>-12.6121</v>
       </c>
       <c r="Q26" t="n">
-        <v>-26.1944</v>
+        <v>-26.19439999999999</v>
       </c>
       <c r="R26" t="n">
         <v>13.5823</v>
       </c>
       <c r="S26" t="n">
-        <v>0.9085999999999996</v>
+        <v>4.245200000000001</v>
       </c>
       <c r="T26" t="n">
         <v>-1.3799</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2884</v>
+        <v>5.6249</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.447699999999999</v>
+        <v>-2.4477</v>
       </c>
       <c r="W26" t="n">
         <v>4.3745</v>
